--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104751_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104751_W33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6937</v>
+        <v>8.739100000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8165</v>
+        <v>6.7677</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8773</v>
+        <v>1.9714</v>
       </c>
       <c r="G2" t="n">
         <v>4.5092</v>
@@ -610,13 +610,13 @@
         <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9034</v>
+        <v>-0.858</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1862</v>
+        <v>-0.2349</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.6231</v>
       </c>
       <c r="V2" t="n">
         <v>3.0392</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.444</v>
+        <v>4.2628</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6589</v>
+        <v>1.7286</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7851</v>
+        <v>2.5342</v>
       </c>
       <c r="G3" t="n">
         <v>2.7237</v>
@@ -688,13 +688,13 @@
         <v>2.9592</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4178</v>
+        <v>-0.5991</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3953</v>
+        <v>-0.3256</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0225</v>
+        <v>-0.2734</v>
       </c>
       <c r="V3" t="n">
         <v>0.5447</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7739</v>
+        <v>2.9691</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7763</v>
+        <v>2.6579</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0025</v>
+        <v>0.3112</v>
       </c>
       <c r="G4" t="n">
         <v>2.5067</v>
@@ -766,13 +766,13 @@
         <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0499</v>
+        <v>-0.8547</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1623</v>
+        <v>0.0439</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2122</v>
+        <v>-0.8986</v>
       </c>
       <c r="V4" t="n">
         <v>1.0895</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2816</v>
+        <v>2.1701</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6379</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6437</v>
+        <v>1.5809</v>
       </c>
       <c r="G5" t="n">
         <v>5.6858</v>
@@ -844,13 +844,13 @@
         <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6224</v>
+        <v>-0.7338</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1862</v>
+        <v>-0.2349</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4362</v>
+        <v>-0.4989</v>
       </c>
       <c r="V5" t="n">
         <v>0.8603</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2243</v>
+        <v>0.2</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3834</v>
+        <v>-2.5018</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6077</v>
+        <v>2.7018</v>
       </c>
       <c r="G6" t="n">
         <v>1.0894</v>
@@ -922,13 +922,13 @@
         <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1822</v>
+        <v>-1.2065</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1862</v>
+        <v>-0.3046</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.996</v>
+        <v>-0.9019</v>
       </c>
       <c r="V6" t="n">
         <v>0.5447</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4342</v>
+        <v>0.0396</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6474</v>
+        <v>1.1212</v>
       </c>
       <c r="F7" t="n">
         <v>-1.0816</v>
@@ -1000,10 +1000,10 @@
         <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3146</v>
+        <v>-0.8408</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6273</v>
+        <v>-0.1535</v>
       </c>
       <c r="U7" t="n">
         <v>-0.6873</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>J. JAWORSKI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9804</v>
+        <v>-1.3582</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1324</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.848</v>
+        <v>-0.5805</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8193</v>
+        <v>-2.6893</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7726</v>
+        <v>-0.4975</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0467</v>
+        <v>-2.1917</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.1566</v>
+        <v>-1.4858</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6516999999999999</v>
+        <v>0.6378</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5048</v>
+        <v>-2.1236</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6628</v>
+        <v>-1.2034</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1209</v>
+        <v>-1.1353</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5419</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3658</v>
+        <v>-0.4553</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3658</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5202</v>
+        <v>-0.5794</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3005</v>
+        <v>-0.0838</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7803</v>
+        <v>-0.4956</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3187</v>
+        <v>0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0895</v>
+        <v>1.2472</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2292</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. JAWORSKI</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0585</v>
+        <v>-2.5586</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3212</v>
+        <v>-1.9615</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7373</v>
+        <v>-0.5971</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6893</v>
+        <v>-3.8193</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4975</v>
+        <v>-1.7726</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1917</v>
+        <v>-2.0467</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4858</v>
+        <v>-2.1566</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6378</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.1236</v>
+        <v>-1.5048</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2034</v>
+        <v>-1.6628</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1353</v>
+        <v>-1.1209</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.5419</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.3658</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.3658</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-0.4553</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.8211</v>
-      </c>
       <c r="S9" t="n">
-        <v>-1.2798</v>
+        <v>-0.058</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6273</v>
+        <v>0.4713</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6524</v>
+        <v>-0.5294</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5447</v>
+        <v>1.3187</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2472</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7025</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6533</v>
+        <v>-2.9357</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.0288</v>
+        <v>-4.8406</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3755</v>
+        <v>1.905</v>
       </c>
       <c r="G10" t="n">
         <v>-1.597</v>
@@ -1234,13 +1234,13 @@
         <v>2.5039</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.671</v>
+        <v>-0.9533</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5347</v>
+        <v>-0.3466</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1362</v>
+        <v>-0.6067</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1578</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3735</v>
+        <v>-4.2621</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9436</v>
+        <v>-2.7067</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4299</v>
+        <v>-1.5554</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4403</v>
@@ -1312,13 +1312,13 @@
         <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0683</v>
+        <v>-0.9568</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4182</v>
+        <v>-0.1813</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.65</v>
+        <v>-0.7755</v>
       </c>
       <c r="V11" t="n">
         <v>-2.6374</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.917599999999998</v>
+        <v>7.2661</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2723999999999984</v>
+        <v>0.07629999999999937</v>
       </c>
       <c r="F12" t="n">
-        <v>7.19</v>
+        <v>7.189899999999999</v>
       </c>
       <c r="G12" t="n">
         <v>8.0283</v>
@@ -1390,13 +1390,13 @@
         <v>19.3486</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.9892</v>
+        <v>-7.640400000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6986</v>
+        <v>-1.35</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.290299999999999</v>
+        <v>-6.2904</v>
       </c>
       <c r="V12" t="n">
         <v>4.601900000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.428800000000001</v>
+        <v>4.8543</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2799</v>
+        <v>3.0819</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1489</v>
+        <v>1.7725</v>
       </c>
       <c r="G13" t="n">
         <v>2.912</v>
@@ -1468,13 +1468,13 @@
         <v>2.2763</v>
       </c>
       <c r="S13" t="n">
-        <v>5.746</v>
+        <v>2.1715</v>
       </c>
       <c r="T13" t="n">
-        <v>5.2901</v>
+        <v>2.0921</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4558</v>
+        <v>0.0795</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2292</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5315</v>
+        <v>1.2735</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8264</v>
+        <v>2.537</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2949</v>
+        <v>-1.2635</v>
       </c>
       <c r="G14" t="n">
         <v>1.4396</v>
@@ -1546,13 +1546,13 @@
         <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4529</v>
+        <v>0.2892</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4182</v>
+        <v>0.2925</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0347</v>
+        <v>-0.0033</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3277</v>
+        <v>1.1151</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1727</v>
+        <v>0.3011</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5004</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-1.5887</v>
@@ -1624,13 +1624,13 @@
         <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1535</v>
+        <v>0.6339</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0468</v>
+        <v>0.427</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1067</v>
+        <v>0.2069</v>
       </c>
       <c r="V15" t="n">
         <v>0.9317</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. BRUNOT</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1084</v>
+        <v>0.721</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2788</v>
+        <v>-0.8431</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3872</v>
+        <v>1.5641</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2593</v>
+        <v>0.0161</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-1.2294</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2593</v>
+        <v>1.2455</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.0735</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-0.669</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.7425</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2593</v>
+        <v>-1.0574</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.5604</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2593</v>
+        <v>-0.497</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.5039</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.151</v>
+        <v>0.4773</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2788</v>
+        <v>0.3597</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1279</v>
+        <v>0.1176</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>K. BRUNOT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1395</v>
+        <v>0.2512</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6722</v>
+        <v>-0.0419</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5327</v>
+        <v>0.2931</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0161</v>
+        <v>0.2593</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2294</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2455</v>
+        <v>0.2593</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0735</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.669</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7425</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0574</v>
+        <v>0.2593</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5604</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.497</v>
+        <v>0.2593</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2276</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2763</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5039</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3832</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4694</v>
+        <v>-0.0419</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0862</v>
+        <v>0.0338</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1683</v>
+        <v>-0.3274</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6627</v>
+        <v>-0.245</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.831</v>
+        <v>-0.0825</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9034</v>
+        <v>-0.1544</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5248</v>
+        <v>1.5802</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6214</v>
+        <v>-1.7346</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3602</v>
+        <v>-0.1039</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9932</v>
+        <v>1.9683</v>
       </c>
       <c r="L18" t="n">
-        <v>0.633</v>
+        <v>-2.0721</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5432</v>
+        <v>-0.0505</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5315</v>
+        <v>-0.3881</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0116</v>
+        <v>0.3375</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9105</v>
+        <v>1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2276</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1382</v>
+        <v>2.7316</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6165</v>
+        <v>0.4109</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1611</v>
+        <v>0.68</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4555</v>
+        <v>-0.2691</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.792</v>
+        <v>-1.9497</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0895</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.8814</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2371</v>
+        <v>-1.0044</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3473</v>
+        <v>0.952</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5843</v>
+        <v>-1.9565</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1544</v>
+        <v>-0.9034</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5802</v>
+        <v>-1.5248</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7346</v>
+        <v>0.6214</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1039</v>
+        <v>-0.3602</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9683</v>
+        <v>-0.9932</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0721</v>
+        <v>0.633</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0505</v>
+        <v>-0.5432</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3881</v>
+        <v>-0.5315</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3375</v>
+        <v>-0.0116</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3658</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3658</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7316</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5013</v>
+        <v>0.7804</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2722</v>
+        <v>0.4504</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7709</v>
+        <v>0.33</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.9497</v>
+        <v>-1.792</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5447</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4945</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3858</v>
+        <v>-1.9888</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1256</v>
+        <v>-3.0071</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7397</v>
+        <v>1.0183</v>
       </c>
       <c r="G20" t="n">
         <v>-4.5258</v>
@@ -2014,13 +2014,13 @@
         <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>2.158</v>
+        <v>1.555</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7614</v>
+        <v>0.8798</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3966</v>
+        <v>0.6752</v>
       </c>
       <c r="V20" t="n">
         <v>0.07140000000000001</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2232</v>
+        <v>-2.7284</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6403</v>
+        <v>-3.5219</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4171</v>
+        <v>0.7935</v>
       </c>
       <c r="G21" t="n">
         <v>0.9661</v>
@@ -2092,13 +2092,13 @@
         <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2738</v>
+        <v>0.7687</v>
       </c>
       <c r="T21" t="n">
-        <v>0.622</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3481</v>
+        <v>0.0283</v>
       </c>
       <c r="V21" t="n">
         <v>0.5447</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.309</v>
+        <v>-3.905</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.569</v>
+        <v>-4.3845</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2599</v>
+        <v>0.4795</v>
       </c>
       <c r="G22" t="n">
         <v>-3.9687</v>
@@ -2170,13 +2170,13 @@
         <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.885</v>
+        <v>0.519</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9758</v>
+        <v>0.2086</v>
       </c>
       <c r="U22" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.3104</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8509</v>
+        <v>-5.1787</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8476</v>
+        <v>-2.0184</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0034</v>
+        <v>-3.1602</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4805</v>
@@ -2248,13 +2248,13 @@
         <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.281</v>
+        <v>0.3913</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6273</v>
+        <v>0.2018</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3463</v>
+        <v>0.1895</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1789</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.917400000000001</v>
+        <v>-6.917599999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.189900000000001</v>
+        <v>-7.1899</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2723</v>
+        <v>0.2722999999999995</v>
       </c>
       <c r="G24" t="n">
         <v>-8.028400000000001</v>
@@ -2305,10 +2305,10 @@
         <v>0.5101000000000002</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3329000000000004</v>
+        <v>-0.3328999999999995</v>
       </c>
       <c r="M24" t="n">
-        <v>-8.205400000000001</v>
+        <v>-8.205399999999999</v>
       </c>
       <c r="N24" t="n">
         <v>-7.1835</v>
@@ -2326,13 +2326,13 @@
         <v>17.0724</v>
       </c>
       <c r="S24" t="n">
-        <v>7.989</v>
+        <v>7.989000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>6.2905</v>
+        <v>6.2904</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6987</v>
+        <v>1.6988</v>
       </c>
       <c r="V24" t="n">
         <v>-4.602</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104751_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104751_W33.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-5.691400000000001</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104751_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-10.2936</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
